--- a/Supplementary_Tables_Fatigue_DBMS_85.xlsx
+++ b/Supplementary_Tables_Fatigue_DBMS_85.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\PycharmProjects\FATIGUE_DBMS\Fatigue_80 sampl``\Fatigue_85_augmented_dataset\07_manuscript_outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\PycharmProjects\FATIGUE_DBMS\Fatigue_80 sampl``\Fatigue_DBMS_Anonymous_Review_Repo\Fatigue-Data-Infrastructure-for-Reliability-Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E346E0B-4015-436C-914D-0B434D473D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9045" yWindow="0" windowWidth="11010" windowHeight="10920" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="S1_Baseline_Properties" sheetId="1" r:id="rId1"/>
